--- a/backend/test_export.xlsx
+++ b/backend/test_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,24 +451,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N22DCCN126</t>
+          <t>N22DCCN6386</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Do Thi Dieu Hang</t>
+          <t>Sinh Viên 6386</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N22DCCN126@student.ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0987654326</t>
-        </is>
-      </c>
+          <t>sv6386@ptit.edu.vn</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>D22CQCNMT01-N</t>
@@ -476,271 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>studying</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>N22DCCN134</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nguyen Le Nhat Huy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N22DCCN134@student.ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0111222344</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>N22DCCN156</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pham Tan Nguyen</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N22DCCN156@student.ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0111222344</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>N22DCCN157</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Phạm Ni</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>N22DCCN157@student.ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0123456789</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>studying</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>N22DCCN160</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Phạm Văn Phú</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N22DCCN160@student.ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0111222333</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>N22DCCN4284</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sinh Viên 4284</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sv4284@ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>N22DCCN4901</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sinh Viên 4901</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sv4901@ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>N22DCCN5865</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sinh Viên 5865</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sv5865@ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>N22DCCN6748</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sinh Viên 6748</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sv6748@ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>D22CQCNMT01-N</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>N22DCCN999</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Test Sinh Vien</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>test@ptit.edu.vn</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>studying</t>
         </is>
       </c>
     </row>
